--- a/results/canaliculi/543-2/measurements.xlsx
+++ b/results/canaliculi/543-2/measurements.xlsx
@@ -433,6 +433,11 @@
           <t>interior_lacuna_count</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>assignment_method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -446,6 +451,11 @@
       <c r="C2" t="n">
         <v>12</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -493,13 +503,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>160.6667</v>
+        <v>71.16670000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>143.5</v>
+        <v>71</v>
       </c>
       <c r="D6" t="n">
-        <v>95.48569999999999</v>
+        <v>43.2642</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -517,13 +527,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>169.0441</v>
+        <v>117.2772</v>
       </c>
       <c r="C7" t="n">
-        <v>164.7777</v>
+        <v>108.0435</v>
       </c>
       <c r="D7" t="n">
-        <v>49.5201</v>
+        <v>47.7939</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -585,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="C2" t="n">
-        <v>27288.211</v>
+        <v>7994.539</v>
       </c>
       <c r="D2" t="n">
-        <v>176.053</v>
+        <v>105.1913</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -607,13 +617,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>429</v>
+        <v>193</v>
       </c>
       <c r="C3" t="n">
-        <v>104777.1896</v>
+        <v>38222.3446</v>
       </c>
       <c r="D3" t="n">
-        <v>244.2359</v>
+        <v>198.0432</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -629,13 +639,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C4" t="n">
-        <v>16473.887</v>
+        <v>4181.3527</v>
       </c>
       <c r="D4" t="n">
-        <v>152.536</v>
+        <v>104.5338</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -651,13 +661,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="C5" t="n">
-        <v>24554.0887</v>
+        <v>4946.0361</v>
       </c>
       <c r="D5" t="n">
-        <v>141.1155</v>
+        <v>71.68170000000001</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -673,13 +683,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>11213.9208</v>
+        <v>2409.7779</v>
       </c>
       <c r="D6" t="n">
-        <v>109.9404</v>
+        <v>75.3056</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -695,13 +705,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="C7" t="n">
-        <v>17806.2768</v>
+        <v>4653.9385</v>
       </c>
       <c r="D7" t="n">
-        <v>153.5024</v>
+        <v>87.81019999999999</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -717,13 +727,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>4186.0025</v>
+        <v>1168.0164</v>
       </c>
       <c r="D8" t="n">
-        <v>89.0639</v>
+        <v>55.6198</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -739,13 +749,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>37474.8421</v>
+        <v>9471.469999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>192.1787</v>
+        <v>111.4291</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -761,13 +771,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="C10" t="n">
-        <v>19128.953</v>
+        <v>15063.3702</v>
       </c>
       <c r="D10" t="n">
-        <v>178.7753</v>
+        <v>198.2022</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -783,13 +793,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>157</v>
+        <v>60</v>
       </c>
       <c r="C11" t="n">
-        <v>35703.9149</v>
+        <v>6653.7408</v>
       </c>
       <c r="D11" t="n">
-        <v>227.4135</v>
+        <v>110.8957</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -805,13 +815,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="C12" t="n">
-        <v>16944.5548</v>
+        <v>8406.277</v>
       </c>
       <c r="D12" t="n">
-        <v>128.3678</v>
+        <v>115.1545</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -827,13 +837,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>206</v>
+        <v>76</v>
       </c>
       <c r="C13" t="n">
-        <v>48481.4961</v>
+        <v>13182.903</v>
       </c>
       <c r="D13" t="n">
-        <v>235.3471</v>
+        <v>173.4593</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>

--- a/results/canaliculi/543-2/measurements.xlsx
+++ b/results/canaliculi/543-2/measurements.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>assignment_method</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>count_mode</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>preprocess_mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -456,91 +466,132 @@
           <t>graph</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tophat</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+          <t>count_mode='edge': one canaliculus = one graph edge (OCY-style); 'path': one canaliculus = one cell-to-tip path (re-counts shared trunks)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>n</t>
+          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>canaliculi_count</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>71.16670000000001</v>
-      </c>
-      <c r="C6" t="n">
-        <v>71</v>
-      </c>
-      <c r="D6" t="n">
-        <v>43.2642</v>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>12</v>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>canaliculi_count</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>37</v>
+      </c>
+      <c r="C7" t="n">
+        <v>29</v>
+      </c>
+      <c r="D7" t="n">
+        <v>26.4953</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_length_px</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1072.3365</v>
+      </c>
+      <c r="C8" t="n">
+        <v>858.7016</v>
+      </c>
+      <c r="D8" t="n">
+        <v>781.1651000000001</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>mean_canaliculus_length_px</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>117.2772</v>
-      </c>
-      <c r="C7" t="n">
-        <v>108.0435</v>
-      </c>
-      <c r="D7" t="n">
-        <v>47.7939</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="B9" t="n">
+        <v>29.4324</v>
+      </c>
+      <c r="C9" t="n">
+        <v>28.9201</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.2832</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>12</v>
       </c>
     </row>
@@ -595,13 +646,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C2" t="n">
-        <v>7994.539</v>
+        <v>2078.8368</v>
       </c>
       <c r="D2" t="n">
-        <v>105.1913</v>
+        <v>25.0462</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -617,13 +668,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>193</v>
+        <v>53</v>
       </c>
       <c r="C3" t="n">
-        <v>38222.3446</v>
+        <v>1498.4499</v>
       </c>
       <c r="D3" t="n">
-        <v>198.0432</v>
+        <v>28.2726</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -639,13 +690,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C4" t="n">
-        <v>4181.3527</v>
+        <v>987.0631</v>
       </c>
       <c r="D4" t="n">
-        <v>104.5338</v>
+        <v>26.6774</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -661,13 +712,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>4946.0361</v>
+        <v>363.9361</v>
       </c>
       <c r="D5" t="n">
-        <v>71.68170000000001</v>
+        <v>17.3303</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -683,13 +734,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>2409.7779</v>
+        <v>240.2082</v>
       </c>
       <c r="D6" t="n">
-        <v>75.3056</v>
+        <v>40.0347</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -705,13 +756,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>4653.9385</v>
+        <v>2145.1677</v>
       </c>
       <c r="D7" t="n">
-        <v>87.81019999999999</v>
+        <v>30.6453</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -727,13 +778,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1168.0164</v>
+        <v>330.1787</v>
       </c>
       <c r="D8" t="n">
-        <v>55.6198</v>
+        <v>27.5149</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -749,13 +800,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>9471.469999999999</v>
+        <v>1685.3616</v>
       </c>
       <c r="D9" t="n">
-        <v>111.4291</v>
+        <v>29.5677</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -771,13 +822,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>15063.3702</v>
+        <v>402.3919</v>
       </c>
       <c r="D10" t="n">
-        <v>198.2022</v>
+        <v>33.5327</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -793,13 +844,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>6653.7408</v>
+        <v>297.865</v>
       </c>
       <c r="D11" t="n">
-        <v>110.8957</v>
+        <v>22.9127</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -815,13 +866,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C12" t="n">
-        <v>8406.277</v>
+        <v>2108.2388</v>
       </c>
       <c r="D12" t="n">
-        <v>115.1545</v>
+        <v>35.1373</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -837,13 +888,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>13182.903</v>
+        <v>730.3402</v>
       </c>
       <c r="D13" t="n">
-        <v>173.4593</v>
+        <v>36.517</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>

--- a/results/canaliculi/543-2/measurements.xlsx
+++ b/results/canaliculi/543-2/measurements.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="per_lacuna" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="field" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="per_lacuna" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -606,6 +607,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>per-field metrics -- independent of the per-lacuna assignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Only ~23% of skeleton length is graph-connected to any lacuna in these 2D</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sections, so per-cell numbers use a quarter of the network. These use all of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>analysed_area_px2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1024241</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_skeleton_length_px</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>40240</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_per_px</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.03928763</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>junction_count</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>452</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>junction_density_per_px2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0004413</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lacuna_count</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lacunae_per_px2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.172e-05</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>skeleton_component_count</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>756</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mean_component_length_px</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>53.2275</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>median_component_length_px</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>17</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/results/canaliculi/543-2/measurements.xlsx
+++ b/results/canaliculi/543-2/measurements.xlsx
@@ -531,13 +531,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>62.3333</v>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>26.4953</v>
+        <v>44.9188</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1072.3365</v>
+        <v>1687.3328</v>
       </c>
       <c r="C8" t="n">
-        <v>858.7016</v>
+        <v>1266.4158</v>
       </c>
       <c r="D8" t="n">
-        <v>781.1651000000001</v>
+        <v>1263.5954</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.4324</v>
+        <v>27.4088</v>
       </c>
       <c r="C9" t="n">
-        <v>28.9201</v>
+        <v>28.085</v>
       </c>
       <c r="D9" t="n">
-        <v>6.2832</v>
+        <v>4.2017</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40240</v>
+        <v>45785</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03928763</v>
+        <v>0.04470139</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>452</v>
+        <v>681</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0004413</v>
+        <v>0.00066488</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>756</v>
+        <v>673</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53.2275</v>
+        <v>68.0312</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -847,13 +847,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C2" t="n">
-        <v>2078.8368</v>
+        <v>1615.5454</v>
       </c>
       <c r="D2" t="n">
-        <v>25.0462</v>
+        <v>22.1308</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -869,13 +869,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="C3" t="n">
-        <v>1498.4499</v>
+        <v>3672.5811</v>
       </c>
       <c r="D3" t="n">
-        <v>28.2726</v>
+        <v>25.1547</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -891,13 +891,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n">
-        <v>987.0631</v>
+        <v>1009.4478</v>
       </c>
       <c r="D4" t="n">
-        <v>26.6774</v>
+        <v>28.8414</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -913,13 +913,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="C5" t="n">
-        <v>363.9361</v>
+        <v>1016.0925</v>
       </c>
       <c r="D5" t="n">
-        <v>17.3303</v>
+        <v>19.5402</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>240.2082</v>
+        <v>509.0021</v>
       </c>
       <c r="D6" t="n">
-        <v>40.0347</v>
+        <v>28.2779</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -957,13 +957,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>2145.1677</v>
+        <v>1516.7392</v>
       </c>
       <c r="D7" t="n">
-        <v>30.6453</v>
+        <v>30.3348</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -979,13 +979,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>330.1787</v>
+        <v>352.664</v>
       </c>
       <c r="D8" t="n">
-        <v>27.5149</v>
+        <v>35.2664</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1001,13 +1001,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="C9" t="n">
-        <v>1685.3616</v>
+        <v>3205.0836</v>
       </c>
       <c r="D9" t="n">
-        <v>29.5677</v>
+        <v>31.1173</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>402.3919</v>
+        <v>568.7595</v>
       </c>
       <c r="D10" t="n">
-        <v>33.5327</v>
+        <v>25.8527</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1045,13 +1045,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>297.865</v>
+        <v>826.2397</v>
       </c>
       <c r="D11" t="n">
-        <v>22.9127</v>
+        <v>25.0376</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1067,13 +1067,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>134</v>
       </c>
       <c r="C12" t="n">
-        <v>2108.2388</v>
+        <v>3947.6004</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1373</v>
+        <v>29.4597</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -1089,13 +1089,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="C13" t="n">
-        <v>730.3402</v>
+        <v>2008.2388</v>
       </c>
       <c r="D13" t="n">
-        <v>36.517</v>
+        <v>27.8922</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
